--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>몬스터 고유 ID</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Prefab/Monster</t>
   </si>
   <si>
+    <t>Monster/Cactus[Catus3_0]</t>
+  </si>
+  <si>
     <t>droptable_cactuslime_01</t>
   </si>
   <si>
@@ -86,6 +89,15 @@
   </si>
   <si>
     <t>좀비가된 카우보이</t>
+  </si>
+  <si>
+    <t>Prefab/Monster_2</t>
+  </si>
+  <si>
+    <t>Monster/Cowbot[cowbombie_0]</t>
+  </si>
+  <si>
+    <t>droptable_cowbombie_01</t>
   </si>
 </sst>
 </file>
@@ -409,7 +421,9 @@
     <col customWidth="1" min="4" max="4" width="17.75"/>
     <col customWidth="1" min="5" max="5" width="26.75"/>
     <col customWidth="1" min="6" max="6" width="23.25"/>
-    <col customWidth="1" min="7" max="26" width="11.0"/>
+    <col customWidth="1" min="7" max="7" width="11.0"/>
+    <col customWidth="1" min="8" max="8" width="26.88"/>
+    <col customWidth="1" min="9" max="26" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -562,9 +576,11 @@
       <c r="G4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>21</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -586,13 +602,13 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
         <v>150.0</v>
@@ -603,9 +619,15 @@
       <c r="F5" s="3">
         <v>2.0</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="G5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>

--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>몬스터 고유 ID</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>DropTableId</t>
+  </si>
+  <si>
+    <t>MonsterExp</t>
   </si>
   <si>
     <t>monster_catussilme_01</t>
@@ -172,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -185,17 +188,20 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,7 +429,8 @@
     <col customWidth="1" min="6" max="6" width="23.25"/>
     <col customWidth="1" min="7" max="7" width="11.0"/>
     <col customWidth="1" min="8" max="8" width="26.88"/>
-    <col customWidth="1" min="9" max="26" width="11.0"/>
+    <col customWidth="1" min="9" max="10" width="21.25"/>
+    <col customWidth="1" min="11" max="26" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -490,7 +497,9 @@
       <c r="I2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="3"/>
+      <c r="J2" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
@@ -509,60 +518,62 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
+      <c r="J3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3">
         <v>100.0</v>
@@ -570,19 +581,21 @@
       <c r="E4" s="3">
         <v>10.0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8">
         <v>3.0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="4">
+        <v>30.0</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -602,13 +615,13 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
         <v>150.0</v>
@@ -619,16 +632,18 @@
       <c r="F5" s="3">
         <v>2.0</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="H5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="4">
+        <v>50.0</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>

--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>몬스터 고유 ID</t>
   </si>
@@ -102,6 +102,42 @@
   <si>
     <t>droptable_cowbombie_01</t>
   </si>
+  <si>
+    <t>monster_maxikeleton_01</t>
+  </si>
+  <si>
+    <t>멕시켈레톤</t>
+  </si>
+  <si>
+    <t>모자를 쓴 스켈레톤</t>
+  </si>
+  <si>
+    <t>Prefab/Monster_3</t>
+  </si>
+  <si>
+    <t>Monster/Skeleton[skeleton_0]</t>
+  </si>
+  <si>
+    <t>droptable_maxikeleton_01</t>
+  </si>
+  <si>
+    <t>monster_deserteagle_01</t>
+  </si>
+  <si>
+    <t>데저트이글</t>
+  </si>
+  <si>
+    <t>사막의 독수리</t>
+  </si>
+  <si>
+    <t>Prefab/Monster_4</t>
+  </si>
+  <si>
+    <t>Monster/Eagle[eagle_0]</t>
+  </si>
+  <si>
+    <t>droptable_deserteagle_01</t>
+  </si>
 </sst>
 </file>
 
@@ -175,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -188,17 +224,11 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -421,13 +451,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.0"/>
-    <col customWidth="1" min="2" max="2" width="17.13"/>
+    <col customWidth="1" min="1" max="1" width="19.75"/>
+    <col customWidth="1" min="2" max="2" width="20.13"/>
     <col customWidth="1" min="3" max="3" width="44.38"/>
     <col customWidth="1" min="4" max="4" width="17.75"/>
     <col customWidth="1" min="5" max="5" width="26.75"/>
     <col customWidth="1" min="6" max="6" width="23.25"/>
-    <col customWidth="1" min="7" max="7" width="11.0"/>
+    <col customWidth="1" min="7" max="7" width="15.88"/>
     <col customWidth="1" min="8" max="8" width="26.88"/>
     <col customWidth="1" min="9" max="10" width="21.25"/>
     <col customWidth="1" min="11" max="26" width="11.0"/>
@@ -497,7 +527,7 @@
       <c r="I2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="3"/>
@@ -518,52 +548,52 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -581,7 +611,7 @@
       <c r="E4" s="3">
         <v>10.0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <v>3.0</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -593,7 +623,7 @@
       <c r="I4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>30.0</v>
       </c>
       <c r="K4" s="3"/>
@@ -641,7 +671,7 @@
       <c r="I5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>50.0</v>
       </c>
       <c r="K5" s="3"/>
@@ -662,16 +692,36 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3">
+        <v>135.0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="3">
+        <v>60.0</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -690,16 +740,36 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="A7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3">
+        <v>90.0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="3">
+        <v>70.0</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>

--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
     <t>몬스터 고유 ID</t>
   </si>
@@ -61,6 +61,9 @@
     <t>IconPath</t>
   </si>
   <si>
+    <t>SilhouetteIconPath</t>
+  </si>
+  <si>
     <t>DropTableId</t>
   </si>
   <si>
@@ -82,6 +85,9 @@
     <t>Monster/Cactus[Catus3_0]</t>
   </si>
   <si>
+    <t>Sprite/Silhouette[Silhouette_3]</t>
+  </si>
+  <si>
     <t>droptable_cactuslime_01</t>
   </si>
   <si>
@@ -98,6 +104,9 @@
   </si>
   <si>
     <t>Monster/Cowbot[cowbombie_0]</t>
+  </si>
+  <si>
+    <t>Sprite/Silhouette[Silhouette_2]</t>
   </si>
   <si>
     <t>droptable_cowbombie_01</t>
@@ -118,6 +127,9 @@
     <t>Monster/Skeleton[skeleton_0]</t>
   </si>
   <si>
+    <t>Sprite/Silhouette[Silhouette_0]</t>
+  </si>
+  <si>
     <t>droptable_maxikeleton_01</t>
   </si>
   <si>
@@ -134,6 +146,9 @@
   </si>
   <si>
     <t>Monster/Eagle[eagle_0]</t>
+  </si>
+  <si>
+    <t>Sprite/Silhouette[Silhouette_1]</t>
   </si>
   <si>
     <t>droptable_deserteagle_01</t>
@@ -211,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -224,11 +239,17 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -459,8 +480,8 @@
     <col customWidth="1" min="6" max="6" width="23.25"/>
     <col customWidth="1" min="7" max="7" width="15.88"/>
     <col customWidth="1" min="8" max="8" width="26.88"/>
-    <col customWidth="1" min="9" max="10" width="21.25"/>
-    <col customWidth="1" min="11" max="26" width="11.0"/>
+    <col customWidth="1" min="9" max="11" width="21.25"/>
+    <col customWidth="1" min="12" max="27" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -498,6 +519,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -524,13 +546,15 @@
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -546,64 +570,68 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
+      <c r="K3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3">
         <v>100.0</v>
@@ -611,22 +639,24 @@
       <c r="E4" s="3">
         <v>10.0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8">
         <v>3.0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="3">
+      <c r="I4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="3">
         <v>30.0</v>
       </c>
-      <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -642,16 +672,17 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3">
         <v>150.0</v>
@@ -663,18 +694,20 @@
         <v>2.0</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>29</v>
+      <c r="I5" s="4" t="s">
+        <v>31</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="3">
         <v>50.0</v>
       </c>
-      <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -690,16 +723,17 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3">
         <v>135.0</v>
@@ -711,18 +745,20 @@
         <v>3.0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>35</v>
+      <c r="I6" s="4" t="s">
+        <v>38</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="3">
         <v>60.0</v>
       </c>
-      <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -738,16 +774,17 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D7" s="3">
         <v>90.0</v>
@@ -759,18 +796,20 @@
         <v>5.0</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>41</v>
+      <c r="I7" s="4" t="s">
+        <v>45</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="3">
         <v>70.0</v>
       </c>
-      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -786,6 +825,7 @@
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>
@@ -814,6 +854,7 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1"/>
@@ -842,6 +883,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
@@ -870,6 +912,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
@@ -898,6 +941,7 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
@@ -926,6 +970,7 @@
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -954,6 +999,7 @@
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -982,6 +1028,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
@@ -1010,6 +1057,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3"/>
@@ -1038,6 +1086,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3"/>
@@ -1066,6 +1115,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3"/>
@@ -1094,6 +1144,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3"/>
@@ -1122,6 +1173,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
@@ -1150,6 +1202,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
@@ -1178,6 +1231,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
@@ -1206,6 +1260,7 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3"/>
@@ -1234,6 +1289,7 @@
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
@@ -1262,6 +1318,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3"/>
@@ -1290,6 +1347,7 @@
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
@@ -1318,6 +1376,7 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
@@ -1346,6 +1405,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
@@ -1374,6 +1434,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
@@ -1402,6 +1463,7 @@
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
@@ -1430,6 +1492,7 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
@@ -1458,6 +1521,7 @@
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
@@ -1486,6 +1550,7 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
@@ -1514,6 +1579,7 @@
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
@@ -1542,6 +1608,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
@@ -1570,6 +1637,7 @@
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
@@ -1598,6 +1666,7 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
@@ -1626,6 +1695,7 @@
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3"/>
@@ -1654,6 +1724,7 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3"/>
@@ -1682,6 +1753,7 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3"/>
@@ -1710,6 +1782,7 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3"/>
@@ -1738,6 +1811,7 @@
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3"/>
@@ -1766,6 +1840,7 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3"/>
@@ -1794,6 +1869,7 @@
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3"/>
@@ -1822,6 +1898,7 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3"/>
@@ -1850,6 +1927,7 @@
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3"/>
@@ -1878,6 +1956,7 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3"/>
@@ -1906,6 +1985,7 @@
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3"/>
@@ -1934,6 +2014,7 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
@@ -1962,6 +2043,7 @@
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3"/>
@@ -1990,6 +2072,7 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
@@ -2018,6 +2101,7 @@
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
@@ -2046,6 +2130,7 @@
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
@@ -2074,6 +2159,7 @@
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
@@ -2102,6 +2188,7 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
@@ -2130,6 +2217,7 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
@@ -2158,6 +2246,7 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
@@ -2186,6 +2275,7 @@
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
@@ -2214,6 +2304,7 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3"/>
@@ -2242,6 +2333,7 @@
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3"/>
@@ -2270,6 +2362,7 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3"/>
@@ -2298,6 +2391,7 @@
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3"/>
@@ -2326,6 +2420,7 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
@@ -2354,6 +2449,7 @@
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3"/>
@@ -2382,6 +2478,7 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3"/>
@@ -2410,6 +2507,7 @@
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
@@ -2438,6 +2536,7 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
@@ -2466,6 +2565,7 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
@@ -2494,6 +2594,7 @@
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
@@ -2522,6 +2623,7 @@
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3"/>
@@ -2550,6 +2652,7 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
+      <c r="AA70" s="3"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3"/>
@@ -2578,6 +2681,7 @@
       <c r="X71" s="3"/>
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
+      <c r="AA71" s="3"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
@@ -2606,6 +2710,7 @@
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
+      <c r="AA72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
@@ -2634,6 +2739,7 @@
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
+      <c r="AA73" s="3"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3"/>
@@ -2662,6 +2768,7 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
+      <c r="AA74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3"/>
@@ -2690,6 +2797,7 @@
       <c r="X75" s="3"/>
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
+      <c r="AA75" s="3"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
@@ -2718,6 +2826,7 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
@@ -2746,6 +2855,7 @@
       <c r="X77" s="3"/>
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
+      <c r="AA77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3"/>
@@ -2774,6 +2884,7 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
+      <c r="AA78" s="3"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
@@ -2802,6 +2913,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
+      <c r="AA79" s="3"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3"/>
@@ -2830,6 +2942,7 @@
       <c r="X80" s="3"/>
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
+      <c r="AA80" s="3"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
@@ -2858,6 +2971,7 @@
       <c r="X81" s="3"/>
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
+      <c r="AA81" s="3"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
@@ -2886,6 +3000,7 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3"/>
@@ -2914,6 +3029,7 @@
       <c r="X83" s="3"/>
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
+      <c r="AA83" s="3"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
@@ -2942,6 +3058,7 @@
       <c r="X84" s="3"/>
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
+      <c r="AA84" s="3"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
@@ -2970,6 +3087,7 @@
       <c r="X85" s="3"/>
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
+      <c r="AA85" s="3"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3"/>
@@ -2998,6 +3116,7 @@
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
+      <c r="AA86" s="3"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
@@ -3026,6 +3145,7 @@
       <c r="X87" s="3"/>
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
+      <c r="AA87" s="3"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
@@ -3054,6 +3174,7 @@
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
+      <c r="AA88" s="3"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3"/>
@@ -3082,6 +3203,7 @@
       <c r="X89" s="3"/>
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
+      <c r="AA89" s="3"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
@@ -3110,6 +3232,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3"/>
@@ -3138,6 +3261,7 @@
       <c r="X91" s="3"/>
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
+      <c r="AA91" s="3"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
@@ -3166,6 +3290,7 @@
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
+      <c r="AA92" s="3"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3"/>
@@ -3194,6 +3319,7 @@
       <c r="X93" s="3"/>
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
+      <c r="AA93" s="3"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3"/>
@@ -3222,6 +3348,7 @@
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
+      <c r="AA94" s="3"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3"/>
@@ -3250,6 +3377,7 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
@@ -3278,6 +3406,7 @@
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
+      <c r="AA96" s="3"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
@@ -3306,6 +3435,7 @@
       <c r="X97" s="3"/>
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
+      <c r="AA97" s="3"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
@@ -3334,6 +3464,7 @@
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
+      <c r="AA98" s="3"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
@@ -3362,6 +3493,7 @@
       <c r="X99" s="3"/>
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
+      <c r="AA99" s="3"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
@@ -3390,6 +3522,7 @@
       <c r="X100" s="3"/>
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
+      <c r="AA100" s="3"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3"/>
@@ -3418,6 +3551,7 @@
       <c r="X101" s="3"/>
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
+      <c r="AA101" s="3"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3"/>
@@ -3446,6 +3580,7 @@
       <c r="X102" s="3"/>
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
+      <c r="AA102" s="3"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3"/>
@@ -3474,6 +3609,7 @@
       <c r="X103" s="3"/>
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
+      <c r="AA103" s="3"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3"/>
@@ -3502,6 +3638,7 @@
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
+      <c r="AA104" s="3"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="3"/>
@@ -3530,6 +3667,7 @@
       <c r="X105" s="3"/>
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
+      <c r="AA105" s="3"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="3"/>
@@ -3558,6 +3696,7 @@
       <c r="X106" s="3"/>
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
+      <c r="AA106" s="3"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="3"/>
@@ -3586,6 +3725,7 @@
       <c r="X107" s="3"/>
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
+      <c r="AA107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="3"/>
@@ -3614,6 +3754,7 @@
       <c r="X108" s="3"/>
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
+      <c r="AA108" s="3"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
@@ -3642,6 +3783,7 @@
       <c r="X109" s="3"/>
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
+      <c r="AA109" s="3"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="3"/>
@@ -3670,6 +3812,7 @@
       <c r="X110" s="3"/>
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
+      <c r="AA110" s="3"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3"/>
@@ -3698,6 +3841,7 @@
       <c r="X111" s="3"/>
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
+      <c r="AA111" s="3"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="3"/>
@@ -3726,6 +3870,7 @@
       <c r="X112" s="3"/>
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
+      <c r="AA112" s="3"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="3"/>
@@ -3754,6 +3899,7 @@
       <c r="X113" s="3"/>
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
+      <c r="AA113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="3"/>
@@ -3782,6 +3928,7 @@
       <c r="X114" s="3"/>
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
+      <c r="AA114" s="3"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="3"/>
@@ -3810,6 +3957,7 @@
       <c r="X115" s="3"/>
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
+      <c r="AA115" s="3"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="3"/>
@@ -3838,6 +3986,7 @@
       <c r="X116" s="3"/>
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
+      <c r="AA116" s="3"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="3"/>
@@ -3866,6 +4015,7 @@
       <c r="X117" s="3"/>
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
+      <c r="AA117" s="3"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="3"/>
@@ -3894,6 +4044,7 @@
       <c r="X118" s="3"/>
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
+      <c r="AA118" s="3"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="3"/>
@@ -3922,6 +4073,7 @@
       <c r="X119" s="3"/>
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
+      <c r="AA119" s="3"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="3"/>
@@ -3950,6 +4102,7 @@
       <c r="X120" s="3"/>
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
+      <c r="AA120" s="3"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
@@ -3978,6 +4131,7 @@
       <c r="X121" s="3"/>
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
+      <c r="AA121" s="3"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="3"/>
@@ -4006,6 +4160,7 @@
       <c r="X122" s="3"/>
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
+      <c r="AA122" s="3"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
@@ -4034,6 +4189,7 @@
       <c r="X123" s="3"/>
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
+      <c r="AA123" s="3"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
@@ -4062,6 +4218,7 @@
       <c r="X124" s="3"/>
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
+      <c r="AA124" s="3"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
@@ -4090,6 +4247,7 @@
       <c r="X125" s="3"/>
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
+      <c r="AA125" s="3"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
@@ -4118,6 +4276,7 @@
       <c r="X126" s="3"/>
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
+      <c r="AA126" s="3"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
@@ -4146,6 +4305,7 @@
       <c r="X127" s="3"/>
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
+      <c r="AA127" s="3"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
@@ -4174,6 +4334,7 @@
       <c r="X128" s="3"/>
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
+      <c r="AA128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="3"/>
@@ -4202,6 +4363,7 @@
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
+      <c r="AA129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
@@ -4230,6 +4392,7 @@
       <c r="X130" s="3"/>
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
+      <c r="AA130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
@@ -4258,6 +4421,7 @@
       <c r="X131" s="3"/>
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
+      <c r="AA131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
@@ -4286,6 +4450,7 @@
       <c r="X132" s="3"/>
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
+      <c r="AA132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="3"/>
@@ -4314,6 +4479,7 @@
       <c r="X133" s="3"/>
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
+      <c r="AA133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="3"/>
@@ -4342,6 +4508,7 @@
       <c r="X134" s="3"/>
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
+      <c r="AA134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
@@ -4370,6 +4537,7 @@
       <c r="X135" s="3"/>
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
+      <c r="AA135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
@@ -4398,6 +4566,7 @@
       <c r="X136" s="3"/>
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
+      <c r="AA136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
@@ -4426,6 +4595,7 @@
       <c r="X137" s="3"/>
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
+      <c r="AA137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="3"/>
@@ -4454,6 +4624,7 @@
       <c r="X138" s="3"/>
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
+      <c r="AA138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
@@ -4482,6 +4653,7 @@
       <c r="X139" s="3"/>
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
+      <c r="AA139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
@@ -4510,6 +4682,7 @@
       <c r="X140" s="3"/>
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
+      <c r="AA140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="3"/>
@@ -4538,6 +4711,7 @@
       <c r="X141" s="3"/>
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
+      <c r="AA141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="3"/>
@@ -4566,6 +4740,7 @@
       <c r="X142" s="3"/>
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
+      <c r="AA142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="3"/>
@@ -4594,6 +4769,7 @@
       <c r="X143" s="3"/>
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
+      <c r="AA143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="3"/>
@@ -4622,6 +4798,7 @@
       <c r="X144" s="3"/>
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
+      <c r="AA144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="3"/>
@@ -4650,6 +4827,7 @@
       <c r="X145" s="3"/>
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
+      <c r="AA145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="3"/>
@@ -4678,6 +4856,7 @@
       <c r="X146" s="3"/>
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
+      <c r="AA146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="3"/>
@@ -4706,6 +4885,7 @@
       <c r="X147" s="3"/>
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
+      <c r="AA147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="3"/>
@@ -4734,6 +4914,7 @@
       <c r="X148" s="3"/>
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
+      <c r="AA148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="3"/>
@@ -4762,6 +4943,7 @@
       <c r="X149" s="3"/>
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
+      <c r="AA149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="3"/>
@@ -4790,6 +4972,7 @@
       <c r="X150" s="3"/>
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
+      <c r="AA150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="3"/>
@@ -4818,6 +5001,7 @@
       <c r="X151" s="3"/>
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
+      <c r="AA151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="3"/>
@@ -4846,6 +5030,7 @@
       <c r="X152" s="3"/>
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
+      <c r="AA152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="3"/>
@@ -4874,6 +5059,7 @@
       <c r="X153" s="3"/>
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
+      <c r="AA153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="3"/>
@@ -4902,6 +5088,7 @@
       <c r="X154" s="3"/>
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
+      <c r="AA154" s="3"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="3"/>
@@ -4930,6 +5117,7 @@
       <c r="X155" s="3"/>
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
+      <c r="AA155" s="3"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="3"/>
@@ -4958,6 +5146,7 @@
       <c r="X156" s="3"/>
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
+      <c r="AA156" s="3"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="3"/>
@@ -4986,6 +5175,7 @@
       <c r="X157" s="3"/>
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
+      <c r="AA157" s="3"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="3"/>
@@ -5014,6 +5204,7 @@
       <c r="X158" s="3"/>
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
+      <c r="AA158" s="3"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="3"/>
@@ -5042,6 +5233,7 @@
       <c r="X159" s="3"/>
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
+      <c r="AA159" s="3"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="3"/>
@@ -5070,6 +5262,7 @@
       <c r="X160" s="3"/>
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
+      <c r="AA160" s="3"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="3"/>
@@ -5098,6 +5291,7 @@
       <c r="X161" s="3"/>
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
+      <c r="AA161" s="3"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="3"/>
@@ -5126,6 +5320,7 @@
       <c r="X162" s="3"/>
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
+      <c r="AA162" s="3"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="3"/>
@@ -5154,6 +5349,7 @@
       <c r="X163" s="3"/>
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
+      <c r="AA163" s="3"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="3"/>
@@ -5182,6 +5378,7 @@
       <c r="X164" s="3"/>
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
+      <c r="AA164" s="3"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="3"/>
@@ -5210,6 +5407,7 @@
       <c r="X165" s="3"/>
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
+      <c r="AA165" s="3"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="3"/>
@@ -5238,6 +5436,7 @@
       <c r="X166" s="3"/>
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
+      <c r="AA166" s="3"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="3"/>
@@ -5266,6 +5465,7 @@
       <c r="X167" s="3"/>
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
+      <c r="AA167" s="3"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="3"/>
@@ -5294,6 +5494,7 @@
       <c r="X168" s="3"/>
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
+      <c r="AA168" s="3"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="3"/>
@@ -5322,6 +5523,7 @@
       <c r="X169" s="3"/>
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
+      <c r="AA169" s="3"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="3"/>
@@ -5350,6 +5552,7 @@
       <c r="X170" s="3"/>
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
+      <c r="AA170" s="3"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="3"/>
@@ -5378,6 +5581,7 @@
       <c r="X171" s="3"/>
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
+      <c r="AA171" s="3"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="3"/>
@@ -5406,6 +5610,7 @@
       <c r="X172" s="3"/>
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
+      <c r="AA172" s="3"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="3"/>
@@ -5434,6 +5639,7 @@
       <c r="X173" s="3"/>
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
+      <c r="AA173" s="3"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="3"/>
@@ -5462,6 +5668,7 @@
       <c r="X174" s="3"/>
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
+      <c r="AA174" s="3"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="3"/>
@@ -5490,6 +5697,7 @@
       <c r="X175" s="3"/>
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
+      <c r="AA175" s="3"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="3"/>
@@ -5518,6 +5726,7 @@
       <c r="X176" s="3"/>
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
+      <c r="AA176" s="3"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="3"/>
@@ -5546,6 +5755,7 @@
       <c r="X177" s="3"/>
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
+      <c r="AA177" s="3"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="3"/>
@@ -5574,6 +5784,7 @@
       <c r="X178" s="3"/>
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
+      <c r="AA178" s="3"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="3"/>
@@ -5602,6 +5813,7 @@
       <c r="X179" s="3"/>
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
+      <c r="AA179" s="3"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="3"/>
@@ -5630,6 +5842,7 @@
       <c r="X180" s="3"/>
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
+      <c r="AA180" s="3"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="3"/>
@@ -5658,6 +5871,7 @@
       <c r="X181" s="3"/>
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
+      <c r="AA181" s="3"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="3"/>
@@ -5686,6 +5900,7 @@
       <c r="X182" s="3"/>
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
+      <c r="AA182" s="3"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="3"/>
@@ -5714,6 +5929,7 @@
       <c r="X183" s="3"/>
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
+      <c r="AA183" s="3"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="3"/>
@@ -5742,6 +5958,7 @@
       <c r="X184" s="3"/>
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
+      <c r="AA184" s="3"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="3"/>
@@ -5770,6 +5987,7 @@
       <c r="X185" s="3"/>
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
+      <c r="AA185" s="3"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="3"/>
@@ -5798,6 +6016,7 @@
       <c r="X186" s="3"/>
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
+      <c r="AA186" s="3"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="3"/>
@@ -5826,6 +6045,7 @@
       <c r="X187" s="3"/>
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
+      <c r="AA187" s="3"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="3"/>
@@ -5854,6 +6074,7 @@
       <c r="X188" s="3"/>
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
+      <c r="AA188" s="3"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="3"/>
@@ -5882,6 +6103,7 @@
       <c r="X189" s="3"/>
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
+      <c r="AA189" s="3"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="3"/>
@@ -5910,6 +6132,7 @@
       <c r="X190" s="3"/>
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
+      <c r="AA190" s="3"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="3"/>
@@ -5938,6 +6161,7 @@
       <c r="X191" s="3"/>
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
+      <c r="AA191" s="3"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="3"/>
@@ -5966,6 +6190,7 @@
       <c r="X192" s="3"/>
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
+      <c r="AA192" s="3"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="3"/>
@@ -5994,6 +6219,7 @@
       <c r="X193" s="3"/>
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
+      <c r="AA193" s="3"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="3"/>
@@ -6022,6 +6248,7 @@
       <c r="X194" s="3"/>
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
+      <c r="AA194" s="3"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="3"/>
@@ -6050,6 +6277,7 @@
       <c r="X195" s="3"/>
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
+      <c r="AA195" s="3"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="3"/>
@@ -6078,6 +6306,7 @@
       <c r="X196" s="3"/>
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
+      <c r="AA196" s="3"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="3"/>
@@ -6106,6 +6335,7 @@
       <c r="X197" s="3"/>
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
+      <c r="AA197" s="3"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="3"/>
@@ -6134,6 +6364,7 @@
       <c r="X198" s="3"/>
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
+      <c r="AA198" s="3"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="3"/>
@@ -6162,6 +6393,7 @@
       <c r="X199" s="3"/>
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
+      <c r="AA199" s="3"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="3"/>
@@ -6190,6 +6422,7 @@
       <c r="X200" s="3"/>
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
+      <c r="AA200" s="3"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="3"/>
@@ -6218,6 +6451,7 @@
       <c r="X201" s="3"/>
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
+      <c r="AA201" s="3"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="3"/>
@@ -6246,6 +6480,7 @@
       <c r="X202" s="3"/>
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
+      <c r="AA202" s="3"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="3"/>
@@ -6274,6 +6509,7 @@
       <c r="X203" s="3"/>
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
+      <c r="AA203" s="3"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="3"/>
@@ -6302,6 +6538,7 @@
       <c r="X204" s="3"/>
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
+      <c r="AA204" s="3"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="3"/>
@@ -6330,6 +6567,7 @@
       <c r="X205" s="3"/>
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
+      <c r="AA205" s="3"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="3"/>
@@ -6358,6 +6596,7 @@
       <c r="X206" s="3"/>
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
+      <c r="AA206" s="3"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="3"/>
@@ -6386,6 +6625,7 @@
       <c r="X207" s="3"/>
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
+      <c r="AA207" s="3"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="3"/>
@@ -6414,6 +6654,7 @@
       <c r="X208" s="3"/>
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
+      <c r="AA208" s="3"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="3"/>
@@ -6442,6 +6683,7 @@
       <c r="X209" s="3"/>
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
+      <c r="AA209" s="3"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="3"/>
@@ -6470,6 +6712,7 @@
       <c r="X210" s="3"/>
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
+      <c r="AA210" s="3"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="3"/>
@@ -6498,6 +6741,7 @@
       <c r="X211" s="3"/>
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
+      <c r="AA211" s="3"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="3"/>
@@ -6526,6 +6770,7 @@
       <c r="X212" s="3"/>
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
+      <c r="AA212" s="3"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="3"/>
@@ -6554,6 +6799,7 @@
       <c r="X213" s="3"/>
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
+      <c r="AA213" s="3"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="3"/>
@@ -6582,6 +6828,7 @@
       <c r="X214" s="3"/>
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
+      <c r="AA214" s="3"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="3"/>
@@ -6610,6 +6857,7 @@
       <c r="X215" s="3"/>
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
+      <c r="AA215" s="3"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="3"/>
@@ -6638,6 +6886,7 @@
       <c r="X216" s="3"/>
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
+      <c r="AA216" s="3"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="3"/>
@@ -6666,6 +6915,7 @@
       <c r="X217" s="3"/>
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
+      <c r="AA217" s="3"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="3"/>
@@ -6694,6 +6944,7 @@
       <c r="X218" s="3"/>
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
+      <c r="AA218" s="3"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="3"/>
@@ -6722,6 +6973,7 @@
       <c r="X219" s="3"/>
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
+      <c r="AA219" s="3"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="3"/>
@@ -6750,6 +7002,7 @@
       <c r="X220" s="3"/>
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
+      <c r="AA220" s="3"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
   <si>
     <t>몬스터 고유 ID</t>
   </si>
@@ -153,6 +153,27 @@
   <si>
     <t>droptable_deserteagle_01</t>
   </si>
+  <si>
+    <t>monster_boss_01</t>
+  </si>
+  <si>
+    <t>텀부리</t>
+  </si>
+  <si>
+    <t>살아움직이는 회전초</t>
+  </si>
+  <si>
+    <t>Prefab/Monster_Boss</t>
+  </si>
+  <si>
+    <t>Sprite/boss[boss_0]</t>
+  </si>
+  <si>
+    <t>Sprite/bosssilhouette[bosssilhouette_1]</t>
+  </si>
+  <si>
+    <t>droptable_boss_01</t>
+  </si>
 </sst>
 </file>
 
@@ -226,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -239,20 +260,17 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -480,7 +498,8 @@
     <col customWidth="1" min="6" max="6" width="23.25"/>
     <col customWidth="1" min="7" max="7" width="15.88"/>
     <col customWidth="1" min="8" max="8" width="26.88"/>
-    <col customWidth="1" min="9" max="11" width="21.25"/>
+    <col customWidth="1" min="9" max="9" width="29.75"/>
+    <col customWidth="1" min="10" max="11" width="21.25"/>
     <col customWidth="1" min="12" max="27" width="11.0"/>
   </cols>
   <sheetData>
@@ -546,7 +565,7 @@
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J2" s="3" t="s">
@@ -573,55 +592,55 @@
       <c r="AA2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -639,7 +658,7 @@
       <c r="E4" s="3">
         <v>10.0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <v>3.0</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -648,7 +667,7 @@
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -699,7 +718,7 @@
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -750,7 +769,7 @@
       <c r="H6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -801,7 +820,7 @@
       <c r="H7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
@@ -828,17 +847,39 @@
       <c r="AA7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="A8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10000.0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>50.0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1000.0</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
